--- a/exports/EICHERMOT_full_report.xlsx
+++ b/exports/EICHERMOT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>5.16</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.38541666666</v>
+        <v>44582.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>2736</v>
+        <v>2710</v>
       </c>
       <c r="I2" t="n">
         <v>2719.332208206802</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.49</v>
+        <v>-4.41</v>
       </c>
       <c r="L2" t="n">
         <v>5.72</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.31</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44606.55208333334</v>
+        <v>44607.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>2565</v>
+        <v>2720.1</v>
       </c>
       <c r="I3" t="n">
         <v>2688.351867452621</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>5.35</v>
+        <v>-0.37</v>
       </c>
       <c r="L3" t="n">
         <v>1.37</v>
@@ -612,7 +647,7 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>5.69</v>
       </c>
       <c r="O3" t="n">
         <v>-0.91</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.78</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44620.55208333334</v>
+        <v>44622.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>2586</v>
+        <v>2538.65</v>
       </c>
       <c r="I4" t="n">
         <v>2571.841514144425</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.93</v>
+        <v>-6.67</v>
       </c>
       <c r="L4" t="n">
         <v>8.449999999999999</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.32</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>2349</v>
+        <v>2454.45</v>
       </c>
       <c r="I5" t="n">
         <v>2430.88285964311</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>7.47</v>
+        <v>3.32</v>
       </c>
       <c r="L5" t="n">
         <v>1.59</v>
@@ -726,7 +785,7 @@
         <v>3.49</v>
       </c>
       <c r="N5" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
         <v>-2.67</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.02</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44680.55208333334</v>
+        <v>44683.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>2631.9</v>
+        <v>2531.9</v>
       </c>
       <c r="I6" t="n">
         <v>2543.780472646583</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K6" t="n">
-        <v>7.23</v>
+        <v>3.16</v>
       </c>
       <c r="L6" t="n">
         <v>5.67</v>
@@ -783,7 +854,7 @@
         <v>0.98</v>
       </c>
       <c r="N6" t="n">
-        <v>3.18</v>
+        <v>3.49</v>
       </c>
       <c r="O6" t="n">
         <v>3.7</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44694.55208333334</v>
+        <v>44697.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2420.5</v>
+        <v>2583.35</v>
       </c>
       <c r="I7" t="n">
         <v>2500.118733720226</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>-2.03</v>
       </c>
       <c r="L7" t="n">
         <v>3.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0.21</v>
+        <v>4.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.07</v>
+        <v>8.49</v>
       </c>
       <c r="O7" t="n">
         <v>-3.49</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.75</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44728.55208333334</v>
+        <v>44729.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>2656.7</v>
+        <v>2611.85</v>
       </c>
       <c r="I8" t="n">
         <v>2620.411582396874</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K8" t="n">
-        <v>2.84</v>
+        <v>1.1</v>
       </c>
       <c r="L8" t="n">
         <v>3.43</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>6.69</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44734.55208333334</v>
+        <v>44735.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>2661</v>
+        <v>2778</v>
       </c>
       <c r="I9" t="n">
         <v>2763.688756017218</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.88</v>
+        <v>-6.36</v>
       </c>
       <c r="L9" t="n">
-        <v>3.87</v>
+        <v>7.46</v>
       </c>
       <c r="M9" t="n">
         <v>0.59</v>
       </c>
       <c r="N9" t="n">
-        <v>2.79</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
         <v>-1.94</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.1</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44802.38541666666</v>
+        <v>44802.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>3306.1</v>
+        <v>3295</v>
       </c>
       <c r="I10" t="n">
         <v>3295.316744509251</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>67</v>
+        <v>67.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>19.01</v>
+        <v>18.61</v>
       </c>
       <c r="L10" t="n">
         <v>4.06</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>6.12</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44813.55208333334</v>
+        <v>44816.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>3470</v>
+        <v>3538.6</v>
       </c>
       <c r="I11" t="n">
         <v>3496.79416392748</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.31</v>
+        <v>-7.39</v>
       </c>
       <c r="L11" t="n">
-        <v>5.71</v>
+        <v>7.44</v>
       </c>
       <c r="M11" t="n">
         <v>1.4</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.48</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>3683</v>
+        <v>3519.9</v>
       </c>
       <c r="I12" t="n">
         <v>3541.08069908619</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>4.08</v>
+        <v>-0.53</v>
       </c>
       <c r="L12" t="n">
         <v>2.45</v>
@@ -1125,7 +1268,7 @@
         <v>1.93</v>
       </c>
       <c r="N12" t="n">
-        <v>2.39</v>
+        <v>4.79</v>
       </c>
       <c r="O12" t="n">
         <v>1.95</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44854.38541666666</v>
+        <v>44854.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>3605</v>
+        <v>3630</v>
       </c>
       <c r="I13" t="n">
         <v>3622.543496197717</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.42</v>
+        <v>-3.13</v>
       </c>
       <c r="L13" t="n">
         <v>7.42</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>5.25</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44875.55208333334</v>
+        <v>44876.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>3700.3</v>
+        <v>3518.05</v>
       </c>
       <c r="I14" t="n">
         <v>3628.163804528793</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>1.94</v>
+        <v>-3.08</v>
       </c>
       <c r="L14" t="n">
-        <v>1.71</v>
+        <v>3.11</v>
       </c>
       <c r="M14" t="n">
         <v>0.91</v>
       </c>
       <c r="N14" t="n">
-        <v>1.69</v>
+        <v>4.9</v>
       </c>
       <c r="O14" t="n">
         <v>0.5</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.99</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44924.38541666666</v>
+        <v>44924.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>3214.95</v>
+        <v>3288</v>
       </c>
       <c r="I15" t="n">
         <v>3283.842096608079</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>8.619999999999999</v>
+        <v>6.54</v>
       </c>
       <c r="L15" t="n">
         <v>6.21</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>6.2</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44936.55208333334</v>
+        <v>44937.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>3169.95</v>
+        <v>3107.9</v>
       </c>
       <c r="I16" t="n">
         <v>3128.585077066426</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.59</v>
+        <v>-5.48</v>
       </c>
       <c r="L16" t="n">
-        <v>4.37</v>
+        <v>5.81</v>
       </c>
       <c r="M16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="N16" t="n">
         <v>2.82</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>5.68</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>3208</v>
+        <v>3325.45</v>
       </c>
       <c r="I17" t="n">
         <v>3241.895470708741</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.22</v>
+        <v>-7</v>
       </c>
       <c r="L17" t="n">
-        <v>5.03</v>
+        <v>7.94</v>
       </c>
       <c r="M17" t="n">
-        <v>0.52</v>
+        <v>2.24</v>
       </c>
       <c r="N17" t="n">
-        <v>1.84</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
         <v>-1.06</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>6.3</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>3210.05</v>
+        <v>3110</v>
       </c>
       <c r="I18" t="n">
         <v>3141.30524298668</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.47</v>
+        <v>-6.48</v>
       </c>
       <c r="L18" t="n">
-        <v>5.43</v>
+        <v>6.72</v>
       </c>
       <c r="M18" t="n">
         <v>1.23</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>6.65</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>2952</v>
+        <v>2999.1</v>
       </c>
       <c r="I19" t="n">
         <v>2979.764609954462</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>5.08</v>
+        <v>3.57</v>
       </c>
       <c r="L19" t="n">
         <v>3.54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.75</v>
+        <v>3.32</v>
       </c>
       <c r="N19" t="n">
         <v>2.79</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.05</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45086.38541666666</v>
+        <v>45086.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>3614.5</v>
+        <v>3586.95</v>
       </c>
       <c r="I20" t="n">
         <v>3603.250737090854</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>67</v>
+        <v>67.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>20.52</v>
+        <v>19.6</v>
       </c>
       <c r="L20" t="n">
         <v>2.55</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>3.91</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45138.38541666666</v>
+        <v>45138.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>3343.6</v>
+        <v>3367.1</v>
       </c>
       <c r="I21" t="n">
         <v>3363.277192106545</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>51.83333333333334</v>
+        <v>52</v>
       </c>
       <c r="K21" t="n">
-        <v>6.78</v>
+        <v>6.13</v>
       </c>
       <c r="L21" t="n">
         <v>2.2</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>3.28</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45154.55208333334</v>
+        <v>45155.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>3320</v>
+        <v>3302.25</v>
       </c>
       <c r="I22" t="n">
         <v>3305.256735675453</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4</v>
+        <v>-1.93</v>
       </c>
       <c r="L22" t="n">
         <v>2.59</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>4.23</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45173.38541666666</v>
+        <v>45173.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>3421.85</v>
+        <v>3426</v>
       </c>
       <c r="I23" t="n">
         <v>3423.292869066373</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.62</v>
+        <v>-3.75</v>
       </c>
       <c r="L23" t="n">
         <v>4.81</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>3.46</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45198.55208333334</v>
+        <v>45202.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3471.6</v>
+        <v>3340.7</v>
       </c>
       <c r="I24" t="n">
         <v>3346.68019186026</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>25</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>1.33</v>
+        <v>-2.49</v>
       </c>
       <c r="L24" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="M24" t="n">
-        <v>0.24</v>
+        <v>1.29</v>
       </c>
       <c r="N24" t="n">
-        <v>1.89</v>
+        <v>3.53</v>
       </c>
       <c r="O24" t="n">
         <v>0.71</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>6.25</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45217.55208333334</v>
+        <v>45218.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>3490</v>
+        <v>3526.65</v>
       </c>
       <c r="I25" t="n">
         <v>3514.470229779399</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.47</v>
+        <v>-5.57</v>
       </c>
       <c r="L25" t="n">
         <v>6.17</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>4.46</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>3438.9</v>
+        <v>3370.4</v>
       </c>
       <c r="I26" t="n">
         <v>3379.807804574337</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.49</v>
+        <v>-4.43</v>
       </c>
       <c r="L26" t="n">
-        <v>2.86</v>
+        <v>4.44</v>
       </c>
       <c r="M26" t="n">
         <v>0.29</v>
       </c>
       <c r="N26" t="n">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="O26" t="n">
         <v>0.06</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>5.02</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45233.55208333334</v>
+        <v>45236.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>3426</v>
+        <v>3536.7</v>
       </c>
       <c r="I27" t="n">
         <v>3427.17769942418</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.65</v>
+        <v>-4.93</v>
       </c>
       <c r="L27" t="n">
-        <v>2.6</v>
+        <v>5.13</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6</v>
+        <v>0.84</v>
       </c>
       <c r="N27" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="O27" t="n">
         <v>-1.52</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.03</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>4053</v>
+        <v>3905</v>
       </c>
       <c r="I28" t="n">
         <v>3929.227600046898</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>14.6</v>
+        <v>10.41</v>
       </c>
       <c r="L28" t="n">
         <v>2.81</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.39</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>3707.75</v>
+        <v>3817.8</v>
       </c>
       <c r="I29" t="n">
         <v>3786.925378798439</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>5.05</v>
+        <v>2.23</v>
       </c>
       <c r="L29" t="n">
         <v>6.99</v>
@@ -2094,7 +2441,7 @@
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.51</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
         <v>-3.55</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.2</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45350.55208333334</v>
+        <v>45351.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>3860</v>
+        <v>3773.5</v>
       </c>
       <c r="I30" t="n">
         <v>3817.483511415634</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K30" t="n">
-        <v>1.11</v>
+        <v>-1.16</v>
       </c>
       <c r="L30" t="n">
         <v>3.06</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>7.23</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45370.55208333334</v>
+        <v>45371.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>3730</v>
+        <v>3871.2</v>
       </c>
       <c r="I31" t="n">
         <v>3865.558311045987</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>1.15</v>
+        <v>-2.59</v>
       </c>
       <c r="L31" t="n">
-        <v>3.09</v>
+        <v>4.41</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>2.44</v>
       </c>
       <c r="N31" t="n">
-        <v>1.07</v>
+        <v>3.89</v>
       </c>
       <c r="O31" t="n">
         <v>-1.55</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.25</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.38541666666</v>
+        <v>45446.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>4674.75</v>
+        <v>4669</v>
       </c>
       <c r="I32" t="n">
         <v>4672.129518795825</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>75</v>
+        <v>75.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>20.76</v>
+        <v>20.61</v>
       </c>
       <c r="L32" t="n">
         <v>1.3</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>5.16</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45454.55208333334</v>
+        <v>45455.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>4757.1</v>
+        <v>4853.45</v>
       </c>
       <c r="I33" t="n">
         <v>4828.630962581787</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.89</v>
+        <v>-3.95</v>
       </c>
       <c r="L33" t="n">
-        <v>3.06</v>
+        <v>4.38</v>
       </c>
       <c r="M33" t="n">
         <v>0.63</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.42</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45470.38541666666</v>
+        <v>45470.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>4730.9</v>
+        <v>4712.05</v>
       </c>
       <c r="I34" t="n">
         <v>4720.758247794734</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.53</v>
+        <v>-2.91</v>
       </c>
       <c r="L34" t="n">
         <v>3.53</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>5.02</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45482.55208333334</v>
+        <v>45483.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>4825</v>
+        <v>4833.05</v>
       </c>
       <c r="I35" t="n">
         <v>4827.514882180758</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.4</v>
+        <v>-2.57</v>
       </c>
       <c r="L35" t="n">
-        <v>2.67</v>
+        <v>5.16</v>
       </c>
       <c r="M35" t="n">
         <v>0.76</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>3.24</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45505.55208333334</v>
+        <v>45506.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>4963.65</v>
+        <v>4731.3</v>
       </c>
       <c r="I36" t="n">
         <v>4769.286216470225</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K36" t="n">
-        <v>2.7</v>
+        <v>-2.11</v>
       </c>
       <c r="L36" t="n">
-        <v>1.52</v>
+        <v>2.26</v>
       </c>
       <c r="M36" t="n">
         <v>2.07</v>
       </c>
       <c r="N36" t="n">
-        <v>1.44</v>
+        <v>5.05</v>
       </c>
       <c r="O36" t="n">
         <v>0.24</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>7.14</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45512.55208333334</v>
+        <v>45513.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>4578</v>
+        <v>4840</v>
       </c>
       <c r="I37" t="n">
         <v>4831.115780734401</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>3.24</v>
+        <v>-2.3</v>
       </c>
       <c r="L37" t="n">
         <v>3.23</v>
       </c>
       <c r="M37" t="n">
-        <v>0.58</v>
+        <v>4.97</v>
       </c>
       <c r="N37" t="n">
-        <v>0.19</v>
+        <v>5.61</v>
       </c>
       <c r="O37" t="n">
         <v>-5.05</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.29</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>4800</v>
+        <v>4754.45</v>
       </c>
       <c r="I38" t="n">
         <v>4777.613779543839</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.83</v>
+        <v>-1.77</v>
       </c>
       <c r="L38" t="n">
         <v>2.56</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>4.5</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>4874</v>
+        <v>4906.65</v>
       </c>
       <c r="I39" t="n">
         <v>4899.013277804452</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.51</v>
+        <v>-3.2</v>
       </c>
       <c r="L39" t="n">
-        <v>2.96</v>
+        <v>3.88</v>
       </c>
       <c r="M39" t="n">
         <v>0.63</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>3.93</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>4977.4</v>
+        <v>4805</v>
       </c>
       <c r="I40" t="n">
         <v>4859.273999496058</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
-        <v>1.44</v>
+        <v>-2.07</v>
       </c>
       <c r="L40" t="n">
-        <v>1.92</v>
+        <v>3.99</v>
       </c>
       <c r="M40" t="n">
-        <v>0.57</v>
+        <v>0.95</v>
       </c>
       <c r="N40" t="n">
-        <v>2.01</v>
+        <v>3.72</v>
       </c>
       <c r="O40" t="n">
         <v>0.5600000000000001</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.95</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45593.55208333334</v>
+        <v>45594.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>4697.95</v>
+        <v>4828.85</v>
       </c>
       <c r="I41" t="n">
         <v>4802.499897046287</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K41" t="n">
-        <v>2.23</v>
+        <v>-0.5</v>
       </c>
       <c r="L41" t="n">
         <v>3.02</v>
@@ -2778,7 +3269,7 @@
         <v>0.76</v>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>3.88</v>
       </c>
       <c r="O41" t="n">
         <v>-3.72</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.14</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>4719</v>
+        <v>4559.05</v>
       </c>
       <c r="I42" t="n">
         <v>4693.744178574953</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.27</v>
+        <v>-5.59</v>
       </c>
       <c r="L42" t="n">
-        <v>2.97</v>
+        <v>6.06</v>
       </c>
       <c r="M42" t="n">
         <v>0.63</v>
       </c>
       <c r="N42" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
         <v>3.88</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>7.36</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45609.55208333334</v>
+        <v>45610.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>4598.8</v>
+        <v>4926.85</v>
       </c>
       <c r="I43" t="n">
         <v>4831.594792908575</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.87</v>
+        <v>-8.07</v>
       </c>
       <c r="L43" t="n">
-        <v>3.53</v>
+        <v>9.08</v>
       </c>
       <c r="M43" t="n">
-        <v>0.01</v>
+        <v>2.75</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="O43" t="n">
         <v>-2.55</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.73</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45643.38541666666</v>
+        <v>45643.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>4792.75</v>
+        <v>4726.95</v>
       </c>
       <c r="I44" t="n">
         <v>4772.351438042981</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.72</v>
+        <v>-4.06</v>
       </c>
       <c r="L44" t="n">
         <v>4.74</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>4.18</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>4867.25</v>
+        <v>5231.2</v>
       </c>
       <c r="I45" t="n">
         <v>4893.31611966126</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.97</v>
+        <v>-10.67</v>
       </c>
       <c r="L45" t="n">
-        <v>4.82</v>
+        <v>10.93</v>
       </c>
       <c r="M45" t="n">
         <v>0.42</v>
       </c>
       <c r="N45" t="n">
-        <v>1.54</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="O45" t="n">
         <v>-1.97</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.83</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45667.55208333334</v>
+        <v>45670.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>5061.45</v>
+        <v>4957.05</v>
       </c>
       <c r="I46" t="n">
         <v>5037.827122693367</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.24</v>
+        <v>-5.24</v>
       </c>
       <c r="L46" t="n">
         <v>6.96</v>
       </c>
       <c r="M46" t="n">
-        <v>0.06</v>
+        <v>1.02</v>
       </c>
       <c r="N46" t="n">
-        <v>1.45</v>
+        <v>2.27</v>
       </c>
       <c r="O46" t="n">
         <v>8.949999999999999</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>5.64</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45680.55208333334</v>
+        <v>45681.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>5118.05</v>
+        <v>5219</v>
       </c>
       <c r="I47" t="n">
         <v>5194.161247932268</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.25</v>
+        <v>-5.28</v>
       </c>
       <c r="L47" t="n">
-        <v>4.05</v>
+        <v>5.4</v>
       </c>
       <c r="M47" t="n">
         <v>0.44</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.34</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>5327.8</v>
+        <v>4983</v>
       </c>
       <c r="I48" t="n">
         <v>5201.030710140083</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>2.08</v>
+        <v>-4.52</v>
       </c>
       <c r="L48" t="n">
-        <v>2.65</v>
+        <v>5.01</v>
       </c>
       <c r="M48" t="n">
-        <v>0.39</v>
+        <v>3.55</v>
       </c>
       <c r="N48" t="n">
-        <v>1.44</v>
+        <v>6.57</v>
       </c>
       <c r="O48" t="n">
         <v>1.41</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45709.55208333334</v>
+        <v>45712.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>4965</v>
+        <v>5048.25</v>
       </c>
       <c r="I49" t="n">
         <v>4977.681755096201</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K49" t="n">
-        <v>0.36</v>
+        <v>-1.31</v>
       </c>
       <c r="L49" t="n">
         <v>3.14</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>6.64</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>5240.25</v>
+        <v>5033.05</v>
       </c>
       <c r="I50" t="n">
         <v>5226.080080326063</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K50" t="n">
-        <v>3.8</v>
+        <v>-0.3</v>
       </c>
       <c r="L50" t="n">
         <v>5.81</v>
       </c>
       <c r="M50" t="n">
-        <v>1.5</v>
+        <v>4.58</v>
       </c>
       <c r="N50" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="O50" t="n">
         <v>1.04</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>7.11</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>5254.95</v>
+        <v>5375.9</v>
       </c>
       <c r="I51" t="n">
         <v>5349.16203791215</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.41</v>
+        <v>-6.81</v>
       </c>
       <c r="L51" t="n">
-        <v>5.78</v>
+        <v>7.47</v>
       </c>
       <c r="M51" t="n">
         <v>1.72</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.32</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45776.55208333334</v>
+        <v>45777.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>5574.5</v>
+        <v>5525</v>
       </c>
       <c r="I52" t="n">
         <v>5558.554598127299</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K52" t="n">
-        <v>3.69</v>
+        <v>2.77</v>
       </c>
       <c r="L52" t="n">
         <v>1.6</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.73</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45793.55208333334</v>
+        <v>45796.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>5509</v>
+        <v>5584</v>
       </c>
       <c r="I53" t="n">
         <v>5558.984991017134</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>0.29</v>
+        <v>-1.07</v>
       </c>
       <c r="L53" t="n">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="M53" t="n">
         <v>3.32</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.28</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45849.55208333334</v>
+        <v>45852.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>5606.5</v>
+        <v>5526</v>
       </c>
       <c r="I54" t="n">
         <v>5551.168529175379</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K54" t="n">
-        <v>0.4</v>
+        <v>-1.04</v>
       </c>
       <c r="L54" t="n">
         <v>6.53</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>3.85</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>5463.5</v>
+        <v>5602</v>
       </c>
       <c r="I55" t="n">
         <v>5552.952063935365</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K55" t="n">
-        <v>1.13</v>
+        <v>-1.38</v>
       </c>
       <c r="L55" t="n">
         <v>2.84</v>
       </c>
       <c r="M55" t="n">
-        <v>0.98</v>
+        <v>1.6</v>
       </c>
       <c r="N55" t="n">
         <v>1.85</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>4.89</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45967.38541666666</v>
+        <v>45967.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>6842.5</v>
+        <v>6810</v>
       </c>
       <c r="I56" t="n">
         <v>6831.587202139397</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>97</v>
+        <v>97.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>22.14</v>
+        <v>21.56</v>
       </c>
       <c r="L56" t="n">
         <v>2.27</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>4.25</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45980.55208333334</v>
+        <v>45981.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>6898</v>
+        <v>7099.5</v>
       </c>
       <c r="I57" t="n">
         <v>6978.182502910019</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.29</v>
+        <v>-4.25</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>4.63</v>
       </c>
       <c r="M57" t="n">
         <v>0.51</v>
       </c>
       <c r="N57" t="n">
-        <v>1.67</v>
+        <v>3.29</v>
       </c>
       <c r="O57" t="n">
         <v>-1.55</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.8</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46035.55208333334</v>
+        <v>46036.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>7383</v>
+        <v>7321</v>
       </c>
       <c r="I58" t="n">
         <v>7333.8215001452</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K58" t="n">
-        <v>3.99</v>
+        <v>3.12</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>3.79</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46063.55208333334</v>
+        <v>46064.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>7310</v>
+        <v>7742</v>
       </c>
       <c r="I59" t="n">
         <v>7317.203394312178</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>0.15</v>
+        <v>-5.75</v>
       </c>
       <c r="L59" t="n">
-        <v>1.31</v>
+        <v>6.61</v>
       </c>
       <c r="M59" t="n">
         <v>3.12</v>
       </c>
       <c r="N59" t="n">
-        <v>3.19</v>
+        <v>6.38</v>
       </c>
       <c r="O59" t="n">
         <v>-0.18</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>6.95</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>8014</v>
+        <v>7768</v>
       </c>
       <c r="I60" t="n">
         <v>7804.138396225833</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K60" t="n">
-        <v>3.51</v>
+        <v>0.34</v>
       </c>
       <c r="L60" t="n">
         <v>3.11</v>
       </c>
       <c r="M60" t="n">
-        <v>0.68</v>
+        <v>2.67</v>
       </c>
       <c r="N60" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="O60" t="n">
         <v>6.38</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>6.62</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>6648</v>
+        <v>7094.5</v>
       </c>
       <c r="I61" t="n">
         <v>6920.199096676466</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K61" t="n">
-        <v>14.42</v>
+        <v>8.67</v>
       </c>
       <c r="L61" t="n">
         <v>2.94</v>
       </c>
       <c r="M61" t="n">
-        <v>2.81</v>
+        <v>3.78</v>
       </c>
       <c r="N61" t="n">
-        <v>3.71</v>
+        <v>7.7</v>
       </c>
       <c r="O61" t="n">
         <v>-2.64</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.85</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46155.38541666666</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>7032</v>
+        <v>6972</v>
       </c>
       <c r="I62" t="n">
         <v>6994.703577522005</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.88</v>
+        <v>-1.73</v>
       </c>
       <c r="L62" t="n">
         <v>3.43</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.93</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>6985</v>
+        <v>7357.5</v>
       </c>
       <c r="I63" t="n">
         <v>7177.056275238304</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.19</v>
+        <v>-5.53</v>
       </c>
       <c r="L63" t="n">
-        <v>2.06</v>
+        <v>5.97</v>
       </c>
       <c r="M63" t="n">
-        <v>0.63</v>
+        <v>3.61</v>
       </c>
       <c r="N63" t="n">
-        <v>1.2</v>
+        <v>6.37</v>
       </c>
       <c r="O63" t="n">
         <v>-2.15</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.33</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46178.38541666666</v>
+        <v>46178.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>7070</v>
+        <v>7051</v>
       </c>
       <c r="I64" t="n">
         <v>7067.42420360797</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.91</v>
+        <v>-4.17</v>
       </c>
       <c r="L64" t="n">
         <v>5.54</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>4.85</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>7300</v>
+        <v>7592</v>
       </c>
       <c r="I65" t="n">
         <v>7356.168377507004</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.53</v>
+        <v>-7.67</v>
       </c>
       <c r="L65" t="n">
-        <v>4.3</v>
+        <v>7.77</v>
       </c>
       <c r="M65" t="n">
         <v>1.51</v>
       </c>
       <c r="N65" t="n">
-        <v>2.19</v>
+        <v>4.64</v>
       </c>
       <c r="O65" t="n">
         <v>-1.25</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>7.37</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46202.55208333334</v>
+        <v>46203.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>7475</v>
+        <v>7133</v>
       </c>
       <c r="I66" t="n">
         <v>7347.539363263286</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.54</v>
+        <v>-6.05</v>
       </c>
       <c r="L66" t="n">
-        <v>4.11</v>
+        <v>8.56</v>
       </c>
       <c r="M66" t="n">
-        <v>0.61</v>
+        <v>1.11</v>
       </c>
       <c r="N66" t="n">
-        <v>1.61</v>
+        <v>4.94</v>
       </c>
       <c r="O66" t="n">
         <v>4.64</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>7.51</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>7461.5</v>
+        <v>7574</v>
       </c>
       <c r="I67" t="n">
         <v>7558.637327248196</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.61</v>
+        <v>-6.18</v>
       </c>
       <c r="L67" t="n">
-        <v>5.12</v>
+        <v>6.59</v>
       </c>
       <c r="M67" t="n">
         <v>1.68</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>5.49</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>7935</v>
+        <v>7570.5</v>
       </c>
       <c r="I68" t="n">
         <v>7880.819254053538</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K68" t="n">
-        <v>4.77</v>
+        <v>-0.05</v>
       </c>
       <c r="L68" t="n">
         <v>5.73</v>
@@ -4317,7 +5132,7 @@
         <v>1.25</v>
       </c>
       <c r="N68" t="n">
-        <v>1.24</v>
+        <v>3.04</v>
       </c>
       <c r="O68" t="n">
         <v>0.64</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.29</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46307.38541666666</v>
+        <v>46307.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>7108</v>
+        <v>7121</v>
       </c>
       <c r="I69" t="n">
         <v>7113.146780498611</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K69" t="n">
-        <v>6.11</v>
+        <v>5.94</v>
       </c>
       <c r="L69" t="n">
         <v>4.26</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,25 +5249,25 @@
         <v>4.58</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46316.55208333334</v>
+        <v>46317.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>7133</v>
+        <v>7062</v>
       </c>
       <c r="I70" t="n">
         <v>7069.303261399142</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K70" t="n">
-        <v>0.17</v>
+        <v>-0.83</v>
       </c>
       <c r="L70" t="n">
         <v>1.26</v>
       </c>
       <c r="M70" t="n">
-        <v>0.32</v>
+        <v>0.63</v>
       </c>
       <c r="N70" t="n">
         <v>2.98</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>10</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7462,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7472,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7482,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7492,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.2</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7502,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52.1</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="11">
@@ -6683,7 +7542,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.83</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.99</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7562,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.63</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7572,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22.14</v>
+        <v>21.56</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7582,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.6</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7592,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.71</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7602,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.23</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7612,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.449999999999999</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7622,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7632,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7642,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.08</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7652,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.58</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7662,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.31</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7672,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.93</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7682,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
